--- a/refactored_complete_comparison_summary.xlsx
+++ b/refactored_complete_comparison_summary.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -475,39 +475,39 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PHCF-BPR</t>
+          <t>KNN+PHCF-BPR</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.911134620470775</v>
+        <v>0.9118399012606896</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0695906432748538</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07749930381509329</v>
+        <v>0.07851680483259431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1728890173360341</v>
+        <v>0.1635509564026555</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>KNN+PHCF-BPR</t>
+          <t>PHCF-BPR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9107819800758178</v>
+        <v>0.9113109406682537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07309941520467837</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07803483066640961</v>
+        <v>0.07571064413169676</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1778204363560833</v>
+        <v>0.1767759583835987</v>
       </c>
     </row>
     <row r="4">
@@ -570,191 +570,172 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SASRec</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9093714184959888</v>
+        <v>0.9088424579035529</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05146198830409356</v>
+        <v>0.04736842105263158</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01575227891017365</v>
+        <v>0.07381848171321855</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09519799483948545</v>
+        <v>0.1482698532230635</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LightFM-WARP</t>
+          <t>KNN+LightFM-WARP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9093714184959887</v>
+        <v>0.9084898175085957</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05087719298245613</v>
+        <v>0.04327485380116958</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06512970460338881</v>
+        <v>0.08007090375511428</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14263999855199</v>
+        <v>0.154037515846408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LightFM-WARP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9088424579035529</v>
+        <v>0.9084898175085957</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04736842105263158</v>
+        <v>0.03976608187134503</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07381848171321855</v>
+        <v>0.07322044427307585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1482698532230635</v>
+        <v>0.1365040979819535</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>KNN+LightFM-WARP</t>
+          <t>DeepFM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9091950982985101</v>
+        <v>0.9077845367186811</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04678362573099415</v>
+        <v>0.03508771929824562</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06107041107041108</v>
+        <v>0.008547008547008546</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1108435849622979</v>
+        <v>0.04898828245851544</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DeepFM</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9077845367186811</v>
+        <v>0.9074318963237239</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03508771929824562</v>
+        <v>0.02865497076023392</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008547008547008546</v>
+        <v>0.006057879742090269</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04898828245851544</v>
+        <v>0.0359376973306668</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>PCA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9074318963237239</v>
+        <v>0.9070792559287666</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02865497076023392</v>
+        <v>0.0280701754385965</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006057879742090269</v>
+        <v>0.01685035237666817</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0359376973306668</v>
+        <v>0.06344999696403116</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PCA</t>
+          <t>NMF</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.9070792559287666</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0280701754385965</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01685035237666817</v>
+        <v>0.03000824711351027</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06344999696403116</v>
+        <v>0.05894087053192933</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>NMF</t>
+          <t>SVD</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9070792559287666</v>
+        <v>0.9065502953363307</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.0216374269005848</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03000824711351027</v>
+        <v>0.01027140500824711</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05894087053192933</v>
+        <v>0.04231320486194662</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>ALS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9065502953363307</v>
+        <v>0.9061976549413736</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0216374269005848</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01027140500824711</v>
+        <v>0.008718377139429771</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04231320486194662</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>ALS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.9065502953363307</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.01812865497076023</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.01703851703851704</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.04287437191942629</v>
+        <v>0.04105686884000813</v>
       </c>
     </row>
   </sheetData>
